--- a/docs/data/jp/xlsx/5257.xlsx
+++ b/docs/data/jp/xlsx/5257.xlsx
@@ -8022,7 +8022,7 @@
     <row r="103">
       <c r="A103" s="20" t="inlineStr">
         <is>
-          <t>Advisory Cost NOE</t>
+          <t>자문 비용</t>
         </is>
       </c>
       <c r="H103" s="22" t="n">
@@ -8035,7 +8035,7 @@
     <row r="104">
       <c r="A104" s="20" t="inlineStr">
         <is>
-          <t>Advisory Fee NOE</t>
+          <t>자문 비용</t>
         </is>
       </c>
       <c r="J104" s="22" t="n">
